--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5126,6 +5126,106 @@
         <v>1.18030309677124</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2110.53</v>
+      </c>
+      <c r="C235" t="n">
+        <v>113856.4503491211</v>
+      </c>
+      <c r="D235" t="n">
+        <v>113856.4503491211</v>
+      </c>
+      <c r="E235" t="n">
+        <v>6881.6201171875</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.175944924354553</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B236" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C236" t="n">
+        <v>113464.33</v>
+      </c>
+      <c r="D236" t="n">
+        <v>113464.33</v>
+      </c>
+      <c r="E236" t="n">
+        <v>6816.6298828125</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1.169727444648743</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B237" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C237" t="n">
+        <v>113635.93</v>
+      </c>
+      <c r="D237" t="n">
+        <v>113635.93</v>
+      </c>
+      <c r="E237" t="n">
+        <v>6869.5</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.161224365234375</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B238" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C238" t="n">
+        <v>113006.73</v>
+      </c>
+      <c r="D238" t="n">
+        <v>113006.73</v>
+      </c>
+      <c r="E238" t="n">
+        <v>6830.7099609375</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.163561820983887</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B239" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C239" t="n">
+        <v>112823.69</v>
+      </c>
+      <c r="D239" t="n">
+        <v>112823.69</v>
+      </c>
+      <c r="E239" t="n">
+        <v>6740.02001953125</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1.1608065366745</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5226,6 +5226,106 @@
         <v>1.1608065366745</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B240" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C240" t="n">
+        <v>112812.2493017578</v>
+      </c>
+      <c r="D240" t="n">
+        <v>112812.2493017578</v>
+      </c>
+      <c r="E240" t="n">
+        <v>6795.990234375</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.152325987815857</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B241" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C241" t="n">
+        <v>111988.57</v>
+      </c>
+      <c r="D241" t="n">
+        <v>111988.57</v>
+      </c>
+      <c r="E241" t="n">
+        <v>6781.47998046875</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.161723494529724</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B242" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C242" t="n">
+        <v>111416.57</v>
+      </c>
+      <c r="D242" t="n">
+        <v>111416.57</v>
+      </c>
+      <c r="E242" t="n">
+        <v>6775.7998046875</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1.161129951477051</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B243" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C243" t="n">
+        <v>110924.65</v>
+      </c>
+      <c r="D243" t="n">
+        <v>110924.65</v>
+      </c>
+      <c r="E243" t="n">
+        <v>6672.6201171875</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.154321193695068</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B244" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C244" t="n">
+        <v>111016.17</v>
+      </c>
+      <c r="D244" t="n">
+        <v>111016.17</v>
+      </c>
+      <c r="E244" t="n">
+        <v>6632.18994140625</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1.152166604995728</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5326,6 +5326,186 @@
         <v>1.152166604995728</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B245" t="n">
+        <v>2256.09</v>
+      </c>
+      <c r="C245" t="n">
+        <v>110988.6048010254</v>
+      </c>
+      <c r="D245" t="n">
+        <v>110988.6048010254</v>
+      </c>
+      <c r="E245" t="n">
+        <v>6699.3798828125</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.143510580062866</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C246" t="n">
+        <v>112001.33</v>
+      </c>
+      <c r="D246" t="n">
+        <v>112001.33</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6716.08984375</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1.149953961372375</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C247" t="n">
+        <v>111101.36</v>
+      </c>
+      <c r="D247" t="n">
+        <v>111101.36</v>
+      </c>
+      <c r="E247" t="n">
+        <v>6624.7001953125</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1.153948187828064</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B248" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C248" t="n">
+        <v>111346.22</v>
+      </c>
+      <c r="D248" t="n">
+        <v>111346.22</v>
+      </c>
+      <c r="E248" t="n">
+        <v>6606.490234375</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1.14644718170166</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B249" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C249" t="n">
+        <v>108992.6</v>
+      </c>
+      <c r="D249" t="n">
+        <v>108992.6</v>
+      </c>
+      <c r="E249" t="n">
+        <v>6506.47998046875</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1.157755732536316</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C250" t="n">
+        <v>110317.9618841553</v>
+      </c>
+      <c r="D250" t="n">
+        <v>110317.9618841553</v>
+      </c>
+      <c r="E250" t="n">
+        <v>6581</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1.156015872955322</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C251" t="n">
+        <v>110769.87</v>
+      </c>
+      <c r="D251" t="n">
+        <v>110769.87</v>
+      </c>
+      <c r="E251" t="n">
+        <v>6556.3701171875</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1.160712242126465</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B252" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C252" t="n">
+        <v>111494.75</v>
+      </c>
+      <c r="D252" t="n">
+        <v>111494.75</v>
+      </c>
+      <c r="E252" t="n">
+        <v>6591.89990234375</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1.16146719455719</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2484.64</v>
+      </c>
+      <c r="C253" t="n">
+        <v>107535.25</v>
+      </c>
+      <c r="D253" t="n">
+        <v>107535.25</v>
+      </c>
+      <c r="E253" t="n">
+        <v>6477.16015625</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1.156149625778198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5506,6 +5506,106 @@
         <v>1.156149625778198</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C254" t="n">
+        <v>106454.8</v>
+      </c>
+      <c r="D254" t="n">
+        <v>106454.8</v>
+      </c>
+      <c r="E254" t="n">
+        <v>6368.85009765625</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1.153509020805359</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C255" t="n">
+        <v>104522.9968383789</v>
+      </c>
+      <c r="D255" t="n">
+        <v>104522.9968383789</v>
+      </c>
+      <c r="E255" t="n">
+        <v>6343.72021484375</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1.149200677871704</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C256" t="n">
+        <v>107268.4</v>
+      </c>
+      <c r="D256" t="n">
+        <v>107268.4</v>
+      </c>
+      <c r="E256" t="n">
+        <v>6528.52001953125</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1.146000385284424</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C257" t="n">
+        <v>109170.2</v>
+      </c>
+      <c r="D257" t="n">
+        <v>109170.2</v>
+      </c>
+      <c r="E257" t="n">
+        <v>6575.31982421875</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1.157420754432678</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C258" t="n">
+        <v>109510.6</v>
+      </c>
+      <c r="D258" t="n">
+        <v>109510.6</v>
+      </c>
+      <c r="E258" t="n">
+        <v>6582.68994140625</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1.159057378768921</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5606,6 +5606,106 @@
         <v>1.159057378768921</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B259" t="n">
+        <v>2047.8</v>
+      </c>
+      <c r="C259" t="n">
+        <v>110288.3310668945</v>
+      </c>
+      <c r="D259" t="n">
+        <v>110288.3310668945</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6611.830078125</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1.150999665260315</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1787.43</v>
+      </c>
+      <c r="C260" t="n">
+        <v>110722.79</v>
+      </c>
+      <c r="D260" t="n">
+        <v>110722.79</v>
+      </c>
+      <c r="E260" t="n">
+        <v>6616.85009765625</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1.154121279716492</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B261" t="n">
+        <v>1787.43</v>
+      </c>
+      <c r="C261" t="n">
+        <v>115250.11</v>
+      </c>
+      <c r="D261" t="n">
+        <v>115250.11</v>
+      </c>
+      <c r="E261" t="n">
+        <v>6782.81005859375</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1.168661236763</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B262" t="n">
+        <v>1787.43</v>
+      </c>
+      <c r="C262" t="n">
+        <v>116460.6</v>
+      </c>
+      <c r="D262" t="n">
+        <v>116460.6</v>
+      </c>
+      <c r="E262" t="n">
+        <v>6824.66015625</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1.16593599319458</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1787.43</v>
+      </c>
+      <c r="C263" t="n">
+        <v>116910.71</v>
+      </c>
+      <c r="D263" t="n">
+        <v>116910.71</v>
+      </c>
+      <c r="E263" t="n">
+        <v>6816.89013671875</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1.16912567615509</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -1,40 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>buying_power</t>
+  </si>
+  <si>
+    <t>portfolio_value</t>
+  </si>
+  <si>
+    <t>SPX USD</t>
+  </si>
+  <si>
+    <t>FX_EURUSD</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,96 +75,38 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -426,5287 +394,5371 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F263"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F268"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>buying_power</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>portfolio_value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SPX USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FX_EURUSD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
         <v>45681</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>100000</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6101.240234375</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1.041601538658142</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
         <v>45684</v>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>100050</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100050</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>6012.27978515625</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1.046758651733398</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
         <v>45685</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>101349</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>101349</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>6067.7001953125</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>1.044506430625916</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
         <v>45686</v>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>101420</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>101420</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>6039.31005859375</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>1.04290509223938</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
         <v>45687</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>103320</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>103320</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>6071.169921875</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>1.042524576187134</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
         <v>45688</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>103205</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>103205</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>6040.52978515625</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1.039727926254272</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
         <v>45691</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>102450</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>102450</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>5994.56982421875</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>1.024779200553894</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
         <v>45692</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>101850</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>101850</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>6037.8798828125</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>1.032737851142883</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
         <v>45693</v>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>102714</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>102714</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>6061.47998046875</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>1.037279844284058</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
         <v>45694</v>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>102800</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>102800</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>6083.56982421875</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>1.040084838867188</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
         <v>45695</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>103074</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>103074</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>6025.990234375</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>1.038572549819946</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
         <v>45698</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>103815.9</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>103815.9</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>6066.43994140625</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>1.031161665916443</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
         <v>45699</v>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>103088</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>103088</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>6068.5</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>1.030152559280396</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:6">
+      <c r="A15" s="2">
         <v>45700</v>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>102600</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>102600</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>6051.97021484375</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1.036494970321655</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:6">
+      <c r="A16" s="2">
         <v>45701</v>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>102650</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>102650</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>6115.06982421875</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>1.039198637008667</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:6">
+      <c r="A17" s="2">
         <v>45702</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>102421</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>102421</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>6114.6298828125</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1.046167373657227</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:6">
+      <c r="A18" s="2">
         <v>45706</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>103331.03</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>103331.03</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>6129.580078125</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>1.048536777496338</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:6">
+      <c r="A19" s="2">
         <v>45707</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>103287.41</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>103287.41</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>6144.14990234375</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>1.044833779335022</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:6">
+      <c r="A20" s="2">
         <v>45708</v>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>101102</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>101102</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>6117.52001953125</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>1.04210090637207</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:6">
+      <c r="A21" s="2">
         <v>45709</v>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>98663.98</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>98663.98</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>6013.1298828125</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>1.050056219100952</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:6">
+      <c r="A22" s="2">
         <v>45712</v>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>98869.50999999999</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>98869.50999999999</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>5983.25</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>1.047482371330261</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:6">
+      <c r="A23" s="2">
         <v>45713</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>99219.11</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>99219.11</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>5955.25</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>1.046134471893311</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:6">
+      <c r="A24" s="2">
         <v>45714</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>98682</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>98682</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>5956.06005859375</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>1.052410006523132</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:6">
+      <c r="A25" s="2">
         <v>45715</v>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>99356</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>99356</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>5861.56982421875</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>1.048877716064453</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:6">
+      <c r="A26" s="2">
         <v>45716</v>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>100791</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>100791</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>5954.5</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>1.039511799812317</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:6">
+      <c r="A27" s="2">
         <v>45719</v>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>99100</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>99100</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>5849.72021484375</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>1.041384696960449</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:6">
+      <c r="A28" s="2">
         <v>45720</v>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>97369</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>97369</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>5778.14990234375</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>1.048503756523132</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:6">
+      <c r="A29" s="2">
         <v>45721</v>
       </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>96456</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>96456</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>5842.6298828125</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>1.062699317932129</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:6">
+      <c r="A30" s="2">
         <v>45722</v>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
         <v>95537.64</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>95537.64</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>5738.52001953125</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>1.079493880271912</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:6">
+      <c r="A31" s="2">
         <v>45723</v>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
         <v>95909.05</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>95909.05</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>5770.2001953125</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>1.078795194625854</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:6">
+      <c r="A32" s="2">
         <v>45726</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
         <v>95195</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>95195</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>5614.56005859375</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>1.086059331893921</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:6">
+      <c r="A33" s="2">
         <v>45727</v>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
         <v>93284.89999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>93284.89999999999</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>5572.06982421875</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>1.083940386772156</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:6">
+      <c r="A34" s="2">
         <v>45728</v>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>93050.05</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>93050.05</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>5599.2998046875</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>1.091417074203491</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:6">
+      <c r="A35" s="2">
         <v>45729</v>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>92843.71000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>92843.71000000001</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>5521.52001953125</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>1.088624954223633</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:6">
+      <c r="A36" s="2">
         <v>45730</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>94223</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>94223</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>5638.93994140625</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>1.085564136505127</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:6">
+      <c r="A37" s="2">
         <v>45733</v>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
         <v>94699.85000000001</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>94699.85000000001</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>5675.1201171875</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>1.088127493858337</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:6">
+      <c r="A38" s="2">
         <v>45734</v>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>93816.37</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>93816.37</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>5614.66015625</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>1.091917634010315</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:6">
+      <c r="A39" s="2">
         <v>45735</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
         <v>94457.69</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>94457.69</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>5675.2900390625</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>1.093948245048523</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:6">
+      <c r="A40" s="2">
         <v>45736</v>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
         <v>94523.23</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>94523.23</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>5662.89013671875</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>1.091190814971924</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:6">
+      <c r="A41" s="2">
         <v>45737</v>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>94634</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>94634</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>5667.56005859375</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>1.085670232772827</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:6">
+      <c r="A42" s="2">
         <v>45740</v>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>95355.8</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>95355.8</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>5767.56982421875</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>1.083576202392578</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:6">
+      <c r="A43" s="2">
         <v>45741</v>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>95294.5</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>95294.5</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>5776.64990234375</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>1.080356955528259</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:6">
+      <c r="A44" s="2">
         <v>45742</v>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
         <v>95889.69</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>95889.69</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>5712.2001953125</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>1.07874870300293</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:6">
+      <c r="A45" s="2">
         <v>45743</v>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
         <v>95932.88</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>95932.88</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>5693.31005859375</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>1.074206113815308</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:6">
+      <c r="A46" s="2">
         <v>45744</v>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
         <v>94827.94</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>94827.94</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>5580.93994140625</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>1.080100178718567</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="47" spans="1:6">
+      <c r="A47" s="2">
         <v>45747</v>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
         <v>95904.49000000001</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>95904.49000000001</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>5611.85009765625</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>1.082391619682312</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:6">
+      <c r="A48" s="2">
         <v>45748</v>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
         <v>95964.91</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>95964.91</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>5633.06982421875</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>1.08188807964325</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:6">
+      <c r="A49" s="2">
         <v>45749</v>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
         <v>95912.99000000001</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>95912.99000000001</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>5670.97021484375</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>1.079598784446716</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:6">
+      <c r="A50" s="2">
         <v>45750</v>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="n">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
         <v>92884.78</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>92884.78</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>5396.52001953125</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>1.090869426727295</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+    <row r="51" spans="1:6">
+      <c r="A51" s="2">
         <v>45751</v>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
         <v>88073.97</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>88073.97</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>5074.080078125</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>1.104374408721924</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:6">
+      <c r="A52" s="2">
         <v>45754</v>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="n">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
         <v>87504.02</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>87504.02</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>5062.25</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>1.098454475402832</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="53" spans="1:6">
+      <c r="A53" s="2">
         <v>45755</v>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
         <v>86320.07000000001</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>86320.07000000001</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>4982.77001953125</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>1.091536164283752</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:6">
+      <c r="A54" s="2">
         <v>45756</v>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
         <v>90796.546</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>90796.546</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>5456.89990234375</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>1.098044395446777</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:6">
+      <c r="A55" s="2">
         <v>45757</v>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
         <v>87523.08</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>87523.08</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>5268.0498046875</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>1.095206260681152</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:6">
+      <c r="A56" s="2">
         <v>45758</v>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="n">
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
         <v>87713.8</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>87713.8</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>5363.35986328125</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>1.125783801078796</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:6">
+      <c r="A57" s="2">
         <v>45761</v>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="n">
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
         <v>88039.11</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>88039.11</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>5405.97021484375</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>1.134314179420471</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:6">
+      <c r="A58" s="2">
         <v>45762</v>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
         <v>88479.7</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>88479.7</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>5396.6298828125</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>1.13396680355072</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:6">
+      <c r="A59" s="2">
         <v>45763</v>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" t="n">
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
         <v>85421.92999999999</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>85421.92999999999</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>5275.7001953125</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>1.12926721572876</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:6">
+      <c r="A60" s="2">
         <v>45764</v>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
         <v>85512.17</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>85512.17</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>5282.7001953125</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>1.139679074287415</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:6">
+      <c r="A61" s="2">
         <v>45769</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
         <v>85290.28999999999</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>85290.28999999999</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>5287.759765625</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>1.151277899742126</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:6">
+      <c r="A62" s="2">
         <v>45770</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>87564.08500000001</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>87564.08500000001</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>5375.85986328125</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>1.135125279426575</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="63" spans="1:6">
+      <c r="A63" s="2">
         <v>45771</v>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" t="n">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
         <v>88670.64999999999</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>88670.64999999999</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>5484.77001953125</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>1.132733702659607</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:6">
+      <c r="A64" s="2">
         <v>45772</v>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" t="n">
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
         <v>90194.36</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>90194.36</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>5525.2099609375</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>1.137190699577332</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="65" spans="1:6">
+      <c r="A65" s="2">
         <v>45775</v>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" t="n">
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
         <v>90163.75999999999</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>90163.75999999999</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>5528.75</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>1.134314179420471</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:6">
+      <c r="A66" s="2">
         <v>45776</v>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" t="n">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
         <v>90883.14999999999</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>90883.14999999999</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>5560.830078125</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>1.14091432094574</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="67" spans="1:6">
+      <c r="A67" s="2">
         <v>45777</v>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" t="n">
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
         <v>92837.61</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>92837.61</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>5569.06005859375</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>1.138926267623901</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:6">
+      <c r="A68" s="2">
         <v>45778</v>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="n">
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
         <v>92837.61</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>92837.61</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>5604.14013671875</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>1.132489919662476</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
+    <row r="69" spans="1:6">
+      <c r="A69" s="2">
         <v>45779</v>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="n">
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
         <v>94402.17</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>94402.17</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>5686.669921875</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>1.129649877548218</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:6">
+      <c r="A70" s="2">
         <v>45782</v>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="n">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
         <v>93992.20699999999</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>93992.20699999999</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>5650.3798828125</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>1.132323265075684</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+    <row r="71" spans="1:6">
+      <c r="A71" s="2">
         <v>45783</v>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
         <v>92714.88</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>92714.88</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>5606.91015625</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>1.13133692741394</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:6">
+      <c r="A72" s="2">
         <v>45784</v>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
         <v>93732.77</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>93732.77</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>5631.27978515625</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>1.134275555610657</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+    <row r="73" spans="1:6">
+      <c r="A73" s="2">
         <v>45785</v>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" t="n">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
         <v>95148.14999999999</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>95148.14999999999</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>5663.93994140625</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>1.13062059879303</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:6">
+      <c r="A74" s="2">
         <v>45786</v>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="n">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
         <v>96265.58</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>96265.58</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>5659.91015625</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>1.122422695159912</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
+    <row r="75" spans="1:6">
+      <c r="A75" s="2">
         <v>45789</v>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
         <v>99170</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>99170</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>5844.18994140625</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>1.12296462059021</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:6">
+      <c r="A76" s="2">
         <v>45790</v>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
         <v>100140.36</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>100140.36</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>5886.5498046875</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>1.109557747840881</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
+    <row r="77" spans="1:6">
+      <c r="A77" s="2">
         <v>45791</v>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="n">
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
         <v>101113.3</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>101113.3</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>5892.580078125</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>1.118555665016174</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:6">
+      <c r="A78" s="2">
         <v>45792</v>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" t="n">
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
         <v>100807.61</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>100807.61</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>5916.93017578125</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>1.118193030357361</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+    <row r="79" spans="1:6">
+      <c r="A79" s="2">
         <v>45793</v>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="n">
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
         <v>101797.34</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>101797.34</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>5958.3798828125</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>1.119269371032715</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:6">
+      <c r="A80" s="2">
         <v>45796</v>
       </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" t="n">
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
         <v>101149.71</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>101149.71</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>5963.60009765625</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>1.11875593662262</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="81" spans="1:6">
+      <c r="A81" s="2">
         <v>45797</v>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" t="n">
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
         <v>100325.34</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>100325.34</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>5940.4599609375</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>1.123342990875244</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:6">
+      <c r="A82" s="2">
         <v>45798</v>
       </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" t="n">
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
         <v>98337.24000000001</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>98337.24000000001</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>5844.60986328125</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>1.128795504570007</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:6">
+      <c r="A83" s="2">
         <v>45799</v>
       </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" t="n">
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
         <v>98951.37</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>98951.37</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>5842.009765625</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>1.133118748664856</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:6">
+      <c r="A84" s="2">
         <v>45800</v>
       </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" t="n">
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
         <v>97591.95</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>97591.95</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>5802.81982421875</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>1.12818431854248</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:6">
+      <c r="A85" s="2">
         <v>45804</v>
       </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" t="n">
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
         <v>100099.84</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>100099.84</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>5921.5400390625</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>1.138848423957825</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
+    <row r="86" spans="1:6">
+      <c r="A86" s="2">
         <v>45805</v>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" t="n">
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
         <v>100053.27</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>100053.27</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>5888.5498046875</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>1.133709788322449</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
+    <row r="87" spans="1:6">
+      <c r="A87" s="2">
         <v>45806</v>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" t="n">
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
         <v>99685.84</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>99685.84</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>5912.169921875</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>1.123368263244629</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
+    <row r="88" spans="1:6">
+      <c r="A88" s="2">
         <v>45807</v>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="n">
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
         <v>99698.50999999999</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>99698.50999999999</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>5911.68994140625</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>1.137837648391724</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
+    <row r="89" spans="1:6">
+      <c r="A89" s="2">
         <v>45810</v>
       </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" t="n">
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
         <v>99750.113</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>99750.113</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>5935.93994140625</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>1.135331511497498</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
+    <row r="90" spans="1:6">
+      <c r="A90" s="2">
         <v>45811</v>
       </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" t="n">
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
         <v>100949.66</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>100949.66</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>5970.3701171875</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>1.145344257354736</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
+    <row r="91" spans="1:6">
+      <c r="A91" s="2">
         <v>45812</v>
       </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" t="n">
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
         <v>100719.605</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>100719.605</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>5970.81005859375</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>1.138446450233459</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
+    <row r="92" spans="1:6">
+      <c r="A92" s="2">
         <v>45813</v>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
         <v>99709.91</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>99709.91</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>5939.2998046875</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>1.142204403877258</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
+    <row r="93" spans="1:6">
+      <c r="A93" s="2">
         <v>45814</v>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="n">
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
         <v>101125.113</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>101125.113</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>6000.35986328125</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>1.145383477210999</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
+    <row r="94" spans="1:6">
+      <c r="A94" s="2">
         <v>45817</v>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" t="n">
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
         <v>100775.47</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>100775.47</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>6005.8798828125</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>1.14078414440155</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
+    <row r="95" spans="1:6">
+      <c r="A95" s="2">
         <v>45818</v>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" t="n">
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
         <v>101300.37</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>101300.37</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>6038.81005859375</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>1.142804861068726</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
+    <row r="96" spans="1:6">
+      <c r="A96" s="2">
         <v>45819</v>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="n">
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
         <v>100379.3</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>100379.3</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>6022.240234375</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>1.143746018409729</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
+    <row r="97" spans="1:6">
+      <c r="A97" s="2">
         <v>45820</v>
       </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" t="n">
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
         <v>99914.08</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>99914.08</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>6045.259765625</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>1.150933384895325</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
+    <row r="98" spans="1:6">
+      <c r="A98" s="2">
         <v>45821</v>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" t="n">
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
         <v>99145.3</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>99145.3</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>5976.97021484375</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>1.160025477409363</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
+    <row r="99" spans="1:6">
+      <c r="A99" s="2">
         <v>45824</v>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
         <v>100104.88</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>100104.88</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>6033.10986328125</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>1.155668497085571</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
+    <row r="100" spans="1:6">
+      <c r="A100" s="2">
         <v>45825</v>
       </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" t="n">
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
         <v>100000.02</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>100000.02</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>5982.72021484375</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>1.155134558677673</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
+    <row r="101" spans="1:6">
+      <c r="A101" s="2">
         <v>45826</v>
       </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="n">
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
         <v>99890.32000000001</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>99890.32000000001</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>5980.8701171875</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>1.148263812065125</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
+    <row r="102" spans="1:6">
+      <c r="A102" s="2">
         <v>45828</v>
       </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" t="n">
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
         <v>98924.14999999999</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>98924.14999999999</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>5967.83984375</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>1.151277899742126</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
+    <row r="103" spans="1:6">
+      <c r="A103" s="2">
         <v>45831</v>
       </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" t="n">
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
         <v>99516.575</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>99516.575</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>6025.169921875</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>1.150086283683777</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
+    <row r="104" spans="1:6">
+      <c r="A104" s="2">
         <v>45832</v>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" t="n">
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
         <v>100109</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>100109</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>6092.18017578125</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>1.159904479980469</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
+    <row r="105" spans="1:6">
+      <c r="A105" s="2">
         <v>45833</v>
       </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" t="n">
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
         <v>99114.17999999999</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>99114.17999999999</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>6092.16015625</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>1.161224365234375</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
+    <row r="106" spans="1:6">
+      <c r="A106" s="2">
         <v>45834</v>
       </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" t="n">
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
         <v>99569.97</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>99569.97</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>6141.02001953125</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>1.168374419212341</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
+    <row r="107" spans="1:6">
+      <c r="A107" s="2">
         <v>45838</v>
       </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" t="n">
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
         <v>99525.38</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>99525.38</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>6204.9501953125</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>1.17274534702301</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
+    <row r="108" spans="1:6">
+      <c r="A108" s="2">
         <v>45839</v>
       </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" t="n">
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
         <v>99605.94</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>99605.94</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108">
         <v>6198.009765625</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>1.178717017173767</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
+    <row r="109" spans="1:6">
+      <c r="A109" s="2">
         <v>45840</v>
       </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" t="n">
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
         <v>99482.5</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>99482.5</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>6227.419921875</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>1.180553913116455</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
+    <row r="110" spans="1:6">
+      <c r="A110" s="2">
         <v>45841</v>
       </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" t="n">
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
         <v>100845.5</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>100845.5</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>6279.35009765625</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>1.18002450466156</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
+    <row r="111" spans="1:6">
+      <c r="A111" s="2">
         <v>45845</v>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="n">
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
         <v>99871.02</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>99871.02</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>6229.97998046875</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>1.178078293800354</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
+    <row r="112" spans="1:6">
+      <c r="A112" s="2">
         <v>45846</v>
       </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="n">
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
         <v>100253.55</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>100253.55</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>6225.52001953125</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>1.173653841018677</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
+    <row r="113" spans="1:6">
+      <c r="A113" s="2">
         <v>45847</v>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
         <v>100907.38</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>100907.38</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>6263.259765625</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>1.172456622123718</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
+    <row r="114" spans="1:6">
+      <c r="A114" s="2">
         <v>45848</v>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="n">
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
         <v>101325.25</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>101325.25</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>6280.4599609375</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>1.17311692237854</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
+    <row r="115" spans="1:6">
+      <c r="A115" s="2">
         <v>45849</v>
       </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" t="n">
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
         <v>100911.53</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>100911.53</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>6259.75</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>1.170274972915649</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
+    <row r="116" spans="1:6">
+      <c r="A116" s="2">
         <v>45852</v>
       </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" t="n">
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
         <v>101383.6</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>101383.6</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>6268.56005859375</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>1.168210625648499</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
+    <row r="117" spans="1:6">
+      <c r="A117" s="2">
         <v>45853</v>
       </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" t="n">
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
         <v>101844.6</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>101844.6</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>6243.759765625</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>1.166629791259766</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
+    <row r="118" spans="1:6">
+      <c r="A118" s="2">
         <v>45854</v>
       </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" t="n">
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
         <v>101815.53</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>101815.53</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>6263.7001953125</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>1.160739183425903</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
+    <row r="119" spans="1:6">
+      <c r="A119" s="2">
         <v>45855</v>
       </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="n">
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
         <v>102852.57</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>102852.57</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>6297.35986328125</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>1.163575410842896</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
+    <row r="120" spans="1:6">
+      <c r="A120" s="2">
         <v>45856</v>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="n">
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
         <v>102685.08</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>102685.08</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>6296.7900390625</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>1.161548137664795</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
+    <row r="121" spans="1:6">
+      <c r="A121" s="2">
         <v>45859</v>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" t="n">
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
         <v>102287.88</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>102287.88</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>6305.60009765625</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>1.163074612617493</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
+    <row r="122" spans="1:6">
+      <c r="A122" s="2">
         <v>45860</v>
       </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" t="n">
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
         <v>101369.99</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>101369.99</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>6309.6201171875</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>1.169453859329224</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
+    <row r="123" spans="1:6">
+      <c r="A123" s="2">
         <v>45861</v>
       </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" t="n">
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
         <v>101908.76</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>101908.76</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>6358.91015625</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>1.17391562461853</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
+    <row r="124" spans="1:6">
+      <c r="A124" s="2">
         <v>45862</v>
       </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="n">
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
         <v>102447.53</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>102447.53</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>6363.35009765625</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>1.17742645740509</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
+    <row r="125" spans="1:6">
+      <c r="A125" s="2">
         <v>45863</v>
       </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="n">
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
         <v>103059.69</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>103059.69</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>6388.64013671875</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>1.175613164901733</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
+    <row r="126" spans="1:6">
+      <c r="A126" s="2">
         <v>45866</v>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="n">
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
         <v>105044.68</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>105044.68</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>6389.77001953125</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>1.175682187080383</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
+    <row r="127" spans="1:6">
+      <c r="A127" s="2">
         <v>45867</v>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="n">
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
         <v>104548.9</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>104548.9</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>6370.85986328125</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>1.159675717353821</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
+    <row r="128" spans="1:6">
+      <c r="A128" s="2">
         <v>45868</v>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
         <v>106784.97</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128">
         <v>106784.97</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128">
         <v>6362.89990234375</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>1.155094504356384</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
+    <row r="129" spans="1:6">
+      <c r="A129" s="2">
         <v>45869</v>
       </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="n">
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
         <v>105819.5</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129">
         <v>105819.5</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129">
         <v>6339.39013671875</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>1.142935514450073</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
+    <row r="130" spans="1:6">
+      <c r="A130" s="2">
         <v>45870</v>
       </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="n">
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
         <v>102797.2</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130">
         <v>102797.2</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130">
         <v>6238.009765625</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130">
         <v>1.142374038696289</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
+    <row r="131" spans="1:6">
+      <c r="A131" s="2">
         <v>45873</v>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="n">
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
         <v>104580.4</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131">
         <v>104580.4</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131">
         <v>6329.93994140625</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>1.158668041229248</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
+    <row r="132" spans="1:6">
+      <c r="A132" s="2">
         <v>45874</v>
       </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" t="n">
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
         <v>103658.35</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132">
         <v>103658.35</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132">
         <v>6299.18994140625</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132">
         <v>1.158412933349609</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
+    <row r="133" spans="1:6">
+      <c r="A133" s="2">
         <v>45875</v>
       </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" t="n">
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
         <v>104185.88</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133">
         <v>104185.88</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133">
         <v>6345.06005859375</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133">
         <v>1.157916665077209</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
+    <row r="134" spans="1:6">
+      <c r="A134" s="2">
         <v>45876</v>
       </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" t="n">
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
         <v>104631.75</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134">
         <v>104631.75</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134">
         <v>6340</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134">
         <v>1.166316747665405</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
+    <row r="135" spans="1:6">
+      <c r="A135" s="2">
         <v>45880</v>
       </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="n">
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
         <v>105089.59</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135">
         <v>105089.59</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135">
         <v>6373.4501953125</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135">
         <v>1.164795279502869</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="136" spans="1:6">
+      <c r="A136" s="2">
         <v>45881</v>
       </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" t="n">
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
         <v>105870.93</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136">
         <v>105870.93</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136">
         <v>6445.759765625</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136">
         <v>1.161844968795776</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="137" spans="1:6">
+      <c r="A137" s="2">
         <v>45882</v>
       </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="n">
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
         <v>105528.45</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137">
         <v>105528.45</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137">
         <v>6466.580078125</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137">
         <v>1.167705893516541</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="138" spans="1:6">
+      <c r="A138" s="2">
         <v>45883</v>
       </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" t="n">
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
         <v>105627.39</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138">
         <v>105627.39</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138">
         <v>6468.5400390625</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138">
         <v>1.171289324760437</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="139" spans="1:6">
+      <c r="A139" s="2">
         <v>45884</v>
       </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" t="n">
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
         <v>105073.88</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139">
         <v>105073.88</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139">
         <v>6449.7998046875</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139">
         <v>1.16513454914093</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="140" spans="1:6">
+      <c r="A140" s="2">
         <v>45887</v>
       </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" t="n">
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
         <v>104985.47</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140">
         <v>104985.47</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140">
         <v>6449.14990234375</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140">
         <v>1.170658707618713</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
+    <row r="141" spans="1:6">
+      <c r="A141" s="2">
         <v>45888</v>
       </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" t="n">
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
         <v>104387.54</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141">
         <v>104387.54</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141">
         <v>6411.3701171875</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141">
         <v>1.166833877563477</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
+    <row r="142" spans="1:6">
+      <c r="A142" s="2">
         <v>45889</v>
       </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" t="n">
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
         <v>103848.3</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142">
         <v>103848.3</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142">
         <v>6395.77978515625</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142">
         <v>1.164252758026123</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="143" spans="1:6">
+      <c r="A143" s="2">
         <v>45890</v>
       </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="n">
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
         <v>104001.53</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143">
         <v>104001.53</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143">
         <v>6370.169921875</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143">
         <v>1.165175199508667</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="144" spans="1:6">
+      <c r="A144" s="2">
         <v>45891</v>
       </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="n">
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
         <v>104552.98</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144">
         <v>104552.98</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144">
         <v>6466.91015625</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144">
         <v>1.16130530834198</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="145" spans="1:6">
+      <c r="A145" s="2">
         <v>45894</v>
       </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" t="n">
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
         <v>105039.49</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145">
         <v>105039.49</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145">
         <v>6439.31982421875</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145">
         <v>1.170960187911987</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="146" spans="1:6">
+      <c r="A146" s="2">
         <v>45895</v>
       </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" t="n">
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
         <v>105105.65</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146">
         <v>105105.65</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146">
         <v>6465.93994140625</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146">
         <v>1.161844968795776</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="147" spans="1:6">
+      <c r="A147" s="2">
         <v>45896</v>
       </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" t="n">
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
         <v>105825.52</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147">
         <v>105825.52</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147">
         <v>6481.39990234375</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147">
         <v>1.163941144943237</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="148" spans="1:6">
+      <c r="A148" s="2">
         <v>45897</v>
       </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
-      <c r="C148" t="n">
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
         <v>106110.4</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148">
         <v>106110.4</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148">
         <v>6501.85986328125</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148">
         <v>1.164795279502869</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="149" spans="1:6">
+      <c r="A149" s="2">
         <v>45898</v>
       </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" t="n">
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
         <v>104866.45</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149">
         <v>104866.45</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149">
         <v>6460.259765625</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149">
         <v>1.168156027793884</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="150" spans="1:6">
+      <c r="A150" s="2">
         <v>45902</v>
       </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
         <v>104301.48</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150">
         <v>104301.48</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150">
         <v>6415.5400390625</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150">
         <v>1.171591281890869</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="151" spans="1:6">
+      <c r="A151" s="2">
         <v>45903</v>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="n">
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
         <v>103832.07</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151">
         <v>103832.07</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151">
         <v>6448.259765625</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151">
         <v>1.163602590560913</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="152" spans="1:6">
+      <c r="A152" s="2">
         <v>45904</v>
       </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
         <v>104970.46</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152">
         <v>104970.46</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152">
         <v>6502.080078125</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152">
         <v>1.16604483127594</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="153" spans="1:6">
+      <c r="A153" s="2">
         <v>45905</v>
       </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="n">
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
         <v>104701.82</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153">
         <v>104701.82</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153">
         <v>6481.5</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153">
         <v>1.165691375732422</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="154" spans="1:6">
+      <c r="A154" s="2">
         <v>45908</v>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="n">
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
         <v>103748.05</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154">
         <v>103748.05</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154">
         <v>6495.14990234375</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154">
         <v>1.171316862106323</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="155" spans="1:6">
+      <c r="A155" s="2">
         <v>45909</v>
       </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" t="n">
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
         <v>104569.53</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155">
         <v>104569.53</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155">
         <v>6512.60986328125</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155">
         <v>1.176913619041443</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+    <row r="156" spans="1:6">
+      <c r="A156" s="2">
         <v>45910</v>
       </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" t="n">
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
         <v>105627.97</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156">
         <v>105627.97</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156">
         <v>6532.0400390625</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156">
         <v>1.170274972915649</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="157" spans="1:6">
+      <c r="A157" s="2">
         <v>45911</v>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" t="n">
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
         <v>105783.89</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157">
         <v>105783.89</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157">
         <v>6587.47021484375</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157">
         <v>1.170343518257141</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="158" spans="1:6">
+      <c r="A158" s="2">
         <v>45912</v>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="n">
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
         <v>105880.95</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158">
         <v>105880.95</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158">
         <v>6584.2900390625</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158">
         <v>1.173474788665771</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+    <row r="159" spans="1:6">
+      <c r="A159" s="2">
         <v>45915</v>
       </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="n">
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
         <v>105867.58</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159">
         <v>105867.58</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159">
         <v>6615.27978515625</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159">
         <v>1.172649145126343</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="160" spans="1:6">
+      <c r="A160" s="2">
         <v>45916</v>
       </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="n">
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
         <v>104980.52</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160">
         <v>104980.52</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160">
         <v>6606.759765625</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160">
         <v>1.176373720169067</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="161" spans="1:6">
+      <c r="A161" s="2">
         <v>45945</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161">
         <v>2025.71</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161">
         <v>100045.71</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161">
         <v>100045.71</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161">
         <v>6671.06005859375</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F161">
         <v>1.160227417945862</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="162" spans="1:6">
+      <c r="A162" s="2">
         <v>45946</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162">
         <v>2025.71</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162">
         <v>99088.91</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162">
         <v>99088.91</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162">
         <v>6629.06982421875</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F162">
         <v>1.164632439613342</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="163" spans="1:6">
+      <c r="A163" s="2">
         <v>45950</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163">
         <v>2025.71</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163">
         <v>100430.51</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163">
         <v>100430.51</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163">
         <v>6735.1298828125</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163">
         <v>1.165745735168457</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="164" spans="1:6">
+      <c r="A164" s="2">
         <v>45952</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164">
         <v>2171.23</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164">
         <v>99902.37</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164">
         <v>99902.37</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164">
         <v>6699.39990234375</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164">
         <v>1.160038948059082</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="165" spans="1:6">
+      <c r="A165" s="2">
         <v>45953</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165">
         <v>2171.23</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165">
         <v>100592.67</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165">
         <v>100592.67</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165">
         <v>6738.43994140625</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165">
         <v>1.160846948623657</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="166" spans="1:6">
+      <c r="A166" s="2">
         <v>45957</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166">
         <v>2171.23</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166">
         <v>102556.19</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166">
         <v>102556.19</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166">
         <v>6875.16015625</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166">
         <v>1.163169384002686</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="167" spans="1:6">
+      <c r="A167" s="2">
         <v>45959</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167">
         <v>2171.23</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167">
         <v>102111.33</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167">
         <v>102111.33</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167">
         <v>6890.58984375</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167">
         <v>1.165786504745483</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="168" spans="1:6">
+      <c r="A168" s="2">
         <v>45960</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168">
         <v>2171.23</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168">
         <v>101551.42</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168">
         <v>101551.42</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168">
         <v>6822.33984375</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168">
         <v>1.160335183143616</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="169" spans="1:6">
+      <c r="A169" s="2">
         <v>45964</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169">
         <v>2171.23</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169">
         <v>102318.42</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169">
         <v>102318.42</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169">
         <v>6851.97021484375</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169">
         <v>1.152804255485535</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="170" spans="1:6">
+      <c r="A170" s="2">
         <v>45965</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170">
         <v>2171.23</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170">
         <v>100554.32</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170">
         <v>100554.32</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170">
         <v>6771.5498046875</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170">
         <v>1.151914477348328</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="171" spans="1:6">
+      <c r="A171" s="2">
         <v>45967</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171">
         <v>2171.23</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171">
         <v>101428.7</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171">
         <v>101428.7</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171">
         <v>6720.31982421875</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171">
         <v>1.149676442146301</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="172" spans="1:6">
+      <c r="A172" s="2">
         <v>45968</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172">
         <v>2171.23</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172">
         <v>102095.99</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172">
         <v>102095.99</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172">
         <v>6728.7998046875</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172">
         <v>1.154921174049377</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="173" spans="1:6">
+      <c r="A173" s="2">
         <v>45971</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173">
         <v>2171.23</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173">
         <v>103008.72</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173">
         <v>103008.72</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173">
         <v>6832.43017578125</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F173">
         <v>1.154387831687927</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="174" spans="1:6">
+      <c r="A174" s="2">
         <v>45973</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174">
         <v>2171.23</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174">
         <v>104013.49</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174">
         <v>104013.49</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174">
         <v>6850.919921875</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F174">
         <v>1.158748626708984</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="175" spans="1:6">
+      <c r="A175" s="2">
         <v>45979</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175">
         <v>2171.23</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175">
         <v>101199.58</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175">
         <v>101199.58</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175">
         <v>6617.31982421875</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F175">
         <v>1.159057378768921</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="176" spans="1:6">
+      <c r="A176" s="2">
         <v>45980</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176">
         <v>2171.23</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176">
         <v>101146.68</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176">
         <v>101146.68</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176">
         <v>6642.16015625</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F176">
         <v>1.158117771148682</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="177" spans="1:6">
+      <c r="A177" s="2">
         <v>45981</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177">
         <v>2094.43</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177">
         <v>100056.94</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177">
         <v>100056.94</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177">
         <v>6538.759765625</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F177">
         <v>1.154068112373352</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="178" spans="1:6">
+      <c r="A178" s="2">
         <v>45982</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178">
         <v>2094.43</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178">
         <v>101189</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178">
         <v>101189</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178">
         <v>6602.990234375</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F178">
         <v>1.15345573425293</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="179" spans="1:6">
+      <c r="A179" s="2">
         <v>45986</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179">
         <v>2094.43</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179">
         <v>102204.68</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179">
         <v>102204.68</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179">
         <v>6765.8798828125</v>
       </c>
-      <c r="F179" t="n">
+      <c r="F179">
         <v>1.152007341384888</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="180" spans="1:6">
+      <c r="A180" s="2">
         <v>45987</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180">
         <v>2094.43</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180">
         <v>102479.76</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180">
         <v>102479.76</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180">
         <v>6812.60986328125</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F180">
         <v>1.156483769416809</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+    <row r="181" spans="1:6">
+      <c r="A181" s="2">
         <v>45989</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181">
         <v>2094.43</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181">
         <v>102424.15</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181">
         <v>102424.15</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181">
         <v>6849.08984375</v>
       </c>
-      <c r="F181" t="n">
+      <c r="F181">
         <v>1.159985184669495</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="182" spans="1:6">
+      <c r="A182" s="2">
         <v>45993</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182">
         <v>2094.43</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182">
         <v>103019.02</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182">
         <v>103019.02</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182">
         <v>6829.3701171875</v>
       </c>
-      <c r="F182" t="n">
+      <c r="F182">
         <v>1.160766124725342</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="183" spans="1:6">
+      <c r="A183" s="2">
         <v>45994</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183">
         <v>2094.43</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183">
         <v>104028.04</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183">
         <v>104028.04</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183">
         <v>6849.72021484375</v>
       </c>
-      <c r="F183" t="n">
+      <c r="F183">
         <v>1.162790656089783</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="184" spans="1:6">
+      <c r="A184" s="2">
         <v>45995</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184">
         <v>2094.43</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184">
         <v>103531.06</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184">
         <v>103531.06</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184">
         <v>6857.1201171875</v>
       </c>
-      <c r="F184" t="n">
+      <c r="F184">
         <v>1.166684150695801</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="185" spans="1:6">
+      <c r="A185" s="2">
         <v>45996</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185">
         <v>2094.43</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C185">
         <v>103982.86</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185">
         <v>103982.86</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185">
         <v>6870.39990234375</v>
       </c>
-      <c r="F185" t="n">
+      <c r="F185">
         <v>1.164279937744141</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+    <row r="186" spans="1:6">
+      <c r="A186" s="2">
         <v>46000</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186">
         <v>2094.43</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186">
         <v>104118.4</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186">
         <v>104118.4</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186">
         <v>6840.509765625</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F186">
         <v>1.164144277572632</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+    <row r="187" spans="1:6">
+      <c r="A187" s="2">
         <v>46001</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187">
         <v>2094.43</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187">
         <v>106211.74</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187">
         <v>106211.74</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187">
         <v>6886.68017578125</v>
       </c>
-      <c r="F187" t="n">
+      <c r="F187">
         <v>1.16283130645752</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+    <row r="188" spans="1:6">
+      <c r="A188" s="2">
         <v>46002</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188">
         <v>2094.43</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188">
         <v>106445.17</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188">
         <v>106445.17</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188">
         <v>6901</v>
       </c>
-      <c r="F188" t="n">
+      <c r="F188">
         <v>1.170124292373657</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+    <row r="189" spans="1:6">
+      <c r="A189" s="2">
         <v>46003</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189">
         <v>2094.43</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189">
         <v>105089.77</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189">
         <v>105089.77</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189">
         <v>6827.41015625</v>
       </c>
-      <c r="F189" t="n">
+      <c r="F189">
         <v>1.173943161964417</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="190" spans="1:6">
+      <c r="A190" s="2">
         <v>46007</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190">
         <v>2094.43</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190">
         <v>103869.91</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190">
         <v>103869.91</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190">
         <v>6800.259765625</v>
       </c>
-      <c r="F190" t="n">
+      <c r="F190">
         <v>1.175461053848267</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="191" spans="1:6">
+      <c r="A191" s="2">
         <v>46008</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191">
         <v>2094.43</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191">
         <v>103026.55</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191">
         <v>103026.55</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191">
         <v>6721.43017578125</v>
       </c>
-      <c r="F191" t="n">
+      <c r="F191">
         <v>1.174950003623962</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="192" spans="1:6">
+      <c r="A192" s="2">
         <v>46009</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192">
         <v>2094.43</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192">
         <v>103847.32</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192">
         <v>103847.32</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192">
         <v>6774.759765625</v>
       </c>
-      <c r="F192" t="n">
+      <c r="F192">
         <v>1.174232602119446</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+    <row r="193" spans="1:6">
+      <c r="A193" s="2">
         <v>46010</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193">
         <v>2094.43</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193">
         <v>104946.7</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193">
         <v>104946.7</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193">
         <v>6834.5</v>
       </c>
-      <c r="F193" t="n">
+      <c r="F193">
         <v>1.172566652297974</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
         <v>46014</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194">
         <v>2094.43</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194">
         <v>105458.74</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194">
         <v>105458.74</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194">
         <v>6909.7900390625</v>
       </c>
-      <c r="F194" t="n">
+      <c r="F194">
         <v>1.176595091819763</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
         <v>46015</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195">
         <v>2094.43</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195">
         <v>106159.03</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195">
         <v>106159.03</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195">
         <v>6932.0498046875</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F195">
         <v>1.179551362991333</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
         <v>46021</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196">
         <v>2094.48</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196">
         <v>105964.5</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196">
         <v>105964.5</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196">
         <v>6896.240234375</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F196">
         <v>1.177287817001343</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
         <v>46022</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197">
         <v>2110.53</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197">
         <v>105002.26</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197">
         <v>105002.26</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197">
         <v>6845.5</v>
       </c>
-      <c r="F197" t="n">
+      <c r="F197">
         <v>1.174729228019714</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
         <v>46024</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198">
         <v>2110.53</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198">
         <v>106646.22</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198">
         <v>106646.22</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198">
         <v>6858.47021484375</v>
       </c>
-      <c r="F198" t="n">
+      <c r="F198">
         <v>1.175046682357788</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
         <v>46028</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199">
         <v>2110.53</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199">
         <v>109563.61</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199">
         <v>109563.61</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199">
         <v>6944.81982421875</v>
       </c>
-      <c r="F199" t="n">
+      <c r="F199">
         <v>1.171495199203491</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
         <v>46029</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200">
         <v>2110.53</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200">
         <v>108549.76</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200">
         <v>108549.76</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200">
         <v>6920.93017578125</v>
       </c>
-      <c r="F200" t="n">
+      <c r="F200">
         <v>1.168825149536133</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
         <v>46030</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201">
         <v>2110.53</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201">
         <v>108992.85</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201">
         <v>108992.85</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201">
         <v>6921.4599609375</v>
       </c>
-      <c r="F201" t="n">
+      <c r="F201">
         <v>1.167678594589233</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
         <v>46031</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202">
         <v>2110.53</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202">
         <v>110434.77</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202">
         <v>110434.77</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202">
         <v>6966.27978515625</v>
       </c>
-      <c r="F202" t="n">
+      <c r="F202">
         <v>1.165786504745483</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
         <v>46035</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203">
         <v>2110.53</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203">
         <v>110006.7</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203">
         <v>110006.7</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203">
         <v>6963.740234375</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F203">
         <v>1.166697859764099</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
         <v>46036</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204">
         <v>2110.53</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204">
         <v>110021.72</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204">
         <v>110021.72</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204">
         <v>6926.60009765625</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F204">
         <v>1.164252758026123</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
         <v>46037</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205">
         <v>2110.53</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205">
         <v>110021.72</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205">
         <v>110021.72</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E205">
         <v>6944.47021484375</v>
       </c>
-      <c r="F205" t="n">
+      <c r="F205">
         <v>1.164632439613342</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
         <v>46038</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206">
         <v>2110.53</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206">
         <v>110622.52</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206">
         <v>110622.52</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206">
         <v>6940.009765625</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F206">
         <v>1.160900831222534</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
         <v>46042</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207">
         <v>2110.53</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207">
         <v>109383.3672497559</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207">
         <v>109383.3672497559</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207">
         <v>6796.85986328125</v>
       </c>
-      <c r="F207" t="n">
+      <c r="F207">
         <v>1.16391396522522</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
         <v>46043</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208">
         <v>2110.53</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208">
         <v>112192.11</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208">
         <v>112192.11</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208">
         <v>6875.6201171875</v>
       </c>
-      <c r="F208" t="n">
+      <c r="F208">
         <v>1.172786593437195</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
         <v>46044</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209">
         <v>2110.53</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209">
         <v>112755.36</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209">
         <v>112755.36</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209">
         <v>6913.35009765625</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F209">
         <v>1.167297005653381</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
         <v>46045</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210">
         <v>2110.53</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210">
         <v>111043.08</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210">
         <v>111043.08</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210">
         <v>6915.60986328125</v>
       </c>
-      <c r="F210" t="n">
+      <c r="F210">
         <v>1.175461053848267</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
         <v>46048</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211">
         <v>2110.53</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211">
         <v>110817.78</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211">
         <v>110817.78</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211">
         <v>6950.22998046875</v>
       </c>
-      <c r="F211" t="n">
+      <c r="F211">
         <v>1.185845732688904</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
         <v>46049</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212">
         <v>2110.53</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212">
         <v>111839.14</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212">
         <v>111839.14</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212">
         <v>6978.60009765625</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F212">
         <v>1.187648415565491</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
         <v>46050</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213">
         <v>2110.53</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213">
         <v>113228.49</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213">
         <v>113228.49</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213">
         <v>6978.02978515625</v>
       </c>
-      <c r="F213" t="n">
+      <c r="F213">
         <v>1.201764225959778</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
         <v>46051</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214">
         <v>2110.53</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C214">
         <v>113611.5</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214">
         <v>113611.5</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214">
         <v>6969.009765625</v>
       </c>
-      <c r="F214" t="n">
+      <c r="F214">
         <v>1.197776913642883</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
         <v>46052</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215">
         <v>2110.53</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215">
         <v>112642.71</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215">
         <v>112642.71</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215">
         <v>6939.02978515625</v>
       </c>
-      <c r="F215" t="n">
+      <c r="F215">
         <v>1.19657301902771</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
         <v>46055</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216">
         <v>2110.53</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216">
         <v>114482.6636669922</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216">
         <v>114482.6636669922</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216">
         <v>6976.43994140625</v>
       </c>
-      <c r="F216" t="n">
+      <c r="F216">
         <v>1.184918284416199</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
         <v>46056</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217">
         <v>2110.53</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217">
         <v>114437.6</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217">
         <v>114437.6</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217">
         <v>6917.81005859375</v>
       </c>
-      <c r="F217" t="n">
+      <c r="F217">
         <v>1.179871439933777</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
         <v>46057</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218">
         <v>2110.53</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C218">
         <v>114107.16</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218">
         <v>114107.16</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218">
         <v>6882.72021484375</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F218">
         <v>1.18161404132843</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
         <v>46058</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219">
         <v>2110.53</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219">
         <v>113371.18</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219">
         <v>113371.18</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219">
         <v>6798.39990234375</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F219">
         <v>1.180163860321045</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
         <v>46059</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220">
         <v>2110.53</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220">
         <v>116172.4136669922</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220">
         <v>116172.4136669922</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220">
         <v>6932.2998046875</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F220">
         <v>1.177786946296692</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
         <v>46062</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221">
         <v>2110.53</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221">
         <v>115759.3613751221</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221">
         <v>115759.3613751221</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221">
         <v>6964.81982421875</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221">
         <v>1.182578206062317</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
         <v>46063</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B222">
         <v>2110.53</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C222">
         <v>115368.84</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222">
         <v>115368.84</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222">
         <v>6941.81005859375</v>
       </c>
-      <c r="F222" t="n">
+      <c r="F222">
         <v>1.190405368804932</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
         <v>46064</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223">
         <v>2110.53</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C223">
         <v>116938.43</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223">
         <v>116938.43</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223">
         <v>6941.47021484375</v>
       </c>
-      <c r="F223" t="n">
+      <c r="F223">
         <v>1.188961744308472</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
         <v>46065</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224">
         <v>2110.53</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C224">
         <v>114662.9</v>
       </c>
-      <c r="D224" t="n">
+      <c r="D224">
         <v>114662.9</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224">
         <v>6832.759765625</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F224">
         <v>1.18760621547699</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
         <v>46066</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225">
         <v>2110.53</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225">
         <v>115932.09</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D225">
         <v>115932.09</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225">
         <v>6836.169921875</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F225">
         <v>1.186844944953918</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
         <v>46070</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226">
         <v>2110.53</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226">
         <v>115398.8845837402</v>
       </c>
-      <c r="D226" t="n">
+      <c r="D226">
         <v>115398.8845837402</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226">
         <v>6843.22021484375</v>
       </c>
-      <c r="F226" t="n">
+      <c r="F226">
         <v>1.184988498687744</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
         <v>46071</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227">
         <v>2110.53</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227">
         <v>116487.83</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D227">
         <v>116487.83</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227">
         <v>6881.31005859375</v>
       </c>
-      <c r="F227" t="n">
+      <c r="F227">
         <v>1.185185194015503</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
         <v>46072</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228">
         <v>2110.53</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228">
         <v>115796.91</v>
       </c>
-      <c r="D228" t="n">
+      <c r="D228">
         <v>115796.91</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228">
         <v>6861.89013671875</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F228">
         <v>1.178883910179138</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
         <v>46073</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229">
         <v>2110.53</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229">
         <v>116577.95</v>
       </c>
-      <c r="D229" t="n">
+      <c r="D229">
         <v>116577.95</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229">
         <v>6909.509765625</v>
       </c>
-      <c r="F229" t="n">
+      <c r="F229">
         <v>1.176913619041443</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
         <v>46076</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230">
         <v>2110.53</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230">
         <v>114940.7741253662</v>
       </c>
-      <c r="D230" t="n">
+      <c r="D230">
         <v>114940.7741253662</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230">
         <v>6837.75</v>
       </c>
-      <c r="F230" t="n">
+      <c r="F230">
         <v>1.183473944664001</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
         <v>46077</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231">
         <v>2110.53</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C231">
         <v>115624.18</v>
       </c>
-      <c r="D231" t="n">
+      <c r="D231">
         <v>115624.18</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231">
         <v>6890.06982421875</v>
       </c>
-      <c r="F231" t="n">
+      <c r="F231">
         <v>1.179384350776672</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
         <v>46078</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232">
         <v>2110.53</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C232">
         <v>116255.02</v>
       </c>
-      <c r="D232" t="n">
+      <c r="D232">
         <v>116255.02</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232">
         <v>6946.1298828125</v>
       </c>
-      <c r="F232" t="n">
+      <c r="F232">
         <v>1.177523374557495</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
         <v>46079</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233">
         <v>2110.53</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C233">
         <v>115601.65</v>
       </c>
-      <c r="D233" t="n">
+      <c r="D233">
         <v>115601.65</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233">
         <v>6908.85986328125</v>
       </c>
-      <c r="F233" t="n">
+      <c r="F233">
         <v>1.181516408920288</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
         <v>46080</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234">
         <v>2110.53</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234">
         <v>115353.82</v>
       </c>
-      <c r="D234" t="n">
+      <c r="D234">
         <v>115353.82</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234">
         <v>6878.8798828125</v>
       </c>
-      <c r="F234" t="n">
+      <c r="F234">
         <v>1.18030309677124</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
         <v>46083</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235">
         <v>2110.53</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C235">
         <v>113856.4503491211</v>
       </c>
-      <c r="D235" t="n">
+      <c r="D235">
         <v>113856.4503491211</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235">
         <v>6881.6201171875</v>
       </c>
-      <c r="F235" t="n">
+      <c r="F235">
         <v>1.175944924354553</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
         <v>46084</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236">
         <v>2256.09</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C236">
         <v>113464.33</v>
       </c>
-      <c r="D236" t="n">
+      <c r="D236">
         <v>113464.33</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236">
         <v>6816.6298828125</v>
       </c>
-      <c r="F236" t="n">
+      <c r="F236">
         <v>1.169727444648743</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
         <v>46085</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237">
         <v>2256.09</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C237">
         <v>113635.93</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D237">
         <v>113635.93</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237">
         <v>6869.5</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F237">
         <v>1.161224365234375</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
         <v>46086</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238">
         <v>2256.09</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C238">
         <v>113006.73</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D238">
         <v>113006.73</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238">
         <v>6830.7099609375</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F238">
         <v>1.163561820983887</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
         <v>46087</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239">
         <v>2256.09</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C239">
         <v>112823.69</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D239">
         <v>112823.69</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239">
         <v>6740.02001953125</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F239">
         <v>1.1608065366745</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
         <v>46090</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240">
         <v>2256.09</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C240">
         <v>112812.2493017578</v>
       </c>
-      <c r="D240" t="n">
+      <c r="D240">
         <v>112812.2493017578</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240">
         <v>6795.990234375</v>
       </c>
-      <c r="F240" t="n">
+      <c r="F240">
         <v>1.152325987815857</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
         <v>46091</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241">
         <v>2256.09</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C241">
         <v>111988.57</v>
       </c>
-      <c r="D241" t="n">
+      <c r="D241">
         <v>111988.57</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241">
         <v>6781.47998046875</v>
       </c>
-      <c r="F241" t="n">
+      <c r="F241">
         <v>1.161723494529724</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
         <v>46092</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242">
         <v>2256.09</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C242">
         <v>111416.57</v>
       </c>
-      <c r="D242" t="n">
+      <c r="D242">
         <v>111416.57</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242">
         <v>6775.7998046875</v>
       </c>
-      <c r="F242" t="n">
+      <c r="F242">
         <v>1.161129951477051</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
         <v>46093</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243">
         <v>2256.09</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C243">
         <v>110924.65</v>
       </c>
-      <c r="D243" t="n">
+      <c r="D243">
         <v>110924.65</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243">
         <v>6672.6201171875</v>
       </c>
-      <c r="F243" t="n">
+      <c r="F243">
         <v>1.154321193695068</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
         <v>46094</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244">
         <v>2256.09</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C244">
         <v>111016.17</v>
       </c>
-      <c r="D244" t="n">
+      <c r="D244">
         <v>111016.17</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244">
         <v>6632.18994140625</v>
       </c>
-      <c r="F244" t="n">
+      <c r="F244">
         <v>1.152166604995728</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
         <v>46097</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245">
         <v>2256.09</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C245">
         <v>110988.6048010254</v>
       </c>
-      <c r="D245" t="n">
+      <c r="D245">
         <v>110988.6048010254</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245">
         <v>6699.3798828125</v>
       </c>
-      <c r="F245" t="n">
+      <c r="F245">
         <v>1.143510580062866</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
         <v>46098</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246">
         <v>2484.64</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C246">
         <v>112001.33</v>
       </c>
-      <c r="D246" t="n">
+      <c r="D246">
         <v>112001.33</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246">
         <v>6716.08984375</v>
       </c>
-      <c r="F246" t="n">
+      <c r="F246">
         <v>1.149953961372375</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
         <v>46099</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247">
         <v>2484.64</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C247">
         <v>111101.36</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D247">
         <v>111101.36</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247">
         <v>6624.7001953125</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F247">
         <v>1.153948187828064</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
         <v>46100</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248">
         <v>2484.64</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C248">
         <v>111346.22</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D248">
         <v>111346.22</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248">
         <v>6606.490234375</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F248">
         <v>1.14644718170166</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
         <v>46101</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249">
         <v>2484.64</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C249">
         <v>108992.6</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D249">
         <v>108992.6</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249">
         <v>6506.47998046875</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F249">
         <v>1.157755732536316</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
         <v>46104</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250">
         <v>2484.64</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C250">
         <v>110317.9618841553</v>
       </c>
-      <c r="D250" t="n">
+      <c r="D250">
         <v>110317.9618841553</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250">
         <v>6581</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250">
         <v>1.156015872955322</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
         <v>46105</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251">
         <v>2484.64</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C251">
         <v>110769.87</v>
       </c>
-      <c r="D251" t="n">
+      <c r="D251">
         <v>110769.87</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251">
         <v>6556.3701171875</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251">
         <v>1.160712242126465</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
         <v>46106</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252">
         <v>2484.64</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C252">
         <v>111494.75</v>
       </c>
-      <c r="D252" t="n">
+      <c r="D252">
         <v>111494.75</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252">
         <v>6591.89990234375</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252">
         <v>1.16146719455719</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
         <v>46107</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253">
         <v>2484.64</v>
       </c>
-      <c r="C253" t="n">
+      <c r="C253">
         <v>107535.25</v>
       </c>
-      <c r="D253" t="n">
+      <c r="D253">
         <v>107535.25</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253">
         <v>6477.16015625</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253">
         <v>1.156149625778198</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
         <v>46108</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254">
         <v>2047.8</v>
       </c>
-      <c r="C254" t="n">
+      <c r="C254">
         <v>106454.8</v>
       </c>
-      <c r="D254" t="n">
+      <c r="D254">
         <v>106454.8</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254">
         <v>6368.85009765625</v>
       </c>
-      <c r="F254" t="n">
+      <c r="F254">
         <v>1.153509020805359</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
         <v>46111</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255">
         <v>2047.8</v>
       </c>
-      <c r="C255" t="n">
+      <c r="C255">
         <v>104522.9968383789</v>
       </c>
-      <c r="D255" t="n">
+      <c r="D255">
         <v>104522.9968383789</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255">
         <v>6343.72021484375</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255">
         <v>1.149200677871704</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
         <v>46112</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256">
         <v>2047.8</v>
       </c>
-      <c r="C256" t="n">
+      <c r="C256">
         <v>107268.4</v>
       </c>
-      <c r="D256" t="n">
+      <c r="D256">
         <v>107268.4</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256">
         <v>6528.52001953125</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256">
         <v>1.146000385284424</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
         <v>46113</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257">
         <v>2047.8</v>
       </c>
-      <c r="C257" t="n">
+      <c r="C257">
         <v>109170.2</v>
       </c>
-      <c r="D257" t="n">
+      <c r="D257">
         <v>109170.2</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257">
         <v>6575.31982421875</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257">
         <v>1.157420754432678</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
         <v>46114</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258">
         <v>2047.8</v>
       </c>
-      <c r="C258" t="n">
+      <c r="C258">
         <v>109510.6</v>
       </c>
-      <c r="D258" t="n">
+      <c r="D258">
         <v>109510.6</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258">
         <v>6582.68994140625</v>
       </c>
-      <c r="F258" t="n">
+      <c r="F258">
         <v>1.159057378768921</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
         <v>46118</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259">
         <v>2047.8</v>
       </c>
-      <c r="C259" t="n">
+      <c r="C259">
         <v>110288.3310668945</v>
       </c>
-      <c r="D259" t="n">
+      <c r="D259">
         <v>110288.3310668945</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259">
         <v>6611.830078125</v>
       </c>
-      <c r="F259" t="n">
+      <c r="F259">
         <v>1.150999665260315</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
         <v>46119</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260">
         <v>1787.43</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C260">
         <v>110722.79</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D260">
         <v>110722.79</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260">
         <v>6616.85009765625</v>
       </c>
-      <c r="F260" t="n">
+      <c r="F260">
         <v>1.154121279716492</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
         <v>46120</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261">
         <v>1787.43</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261">
         <v>115250.11</v>
       </c>
-      <c r="D261" t="n">
+      <c r="D261">
         <v>115250.11</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261">
         <v>6782.81005859375</v>
       </c>
-      <c r="F261" t="n">
+      <c r="F261">
         <v>1.168661236763</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
         <v>46121</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262">
         <v>1787.43</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C262">
         <v>116460.6</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D262">
         <v>116460.6</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262">
         <v>6824.66015625</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F262">
         <v>1.16593599319458</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
         <v>46122</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263">
         <v>1787.43</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C263">
         <v>116910.71</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D263">
         <v>116910.71</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263">
         <v>6816.89013671875</v>
       </c>
-      <c r="F263" t="n">
+      <c r="F263">
         <v>1.16912567615509</v>
       </c>
     </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B264">
+        <v>1787.43</v>
+      </c>
+      <c r="C264">
+        <v>118051.2746655273</v>
+      </c>
+      <c r="D264">
+        <v>118051.2746655273</v>
+      </c>
+      <c r="E264">
+        <v>6886.240234375</v>
+      </c>
+      <c r="F264">
+        <v>1.16751503944397</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B265">
+        <v>1787.43</v>
+      </c>
+      <c r="C265">
+        <v>119921.64</v>
+      </c>
+      <c r="D265">
+        <v>119921.64</v>
+      </c>
+      <c r="E265">
+        <v>6967.3798828125</v>
+      </c>
+      <c r="F265">
+        <v>1.176885962486267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B266">
+        <v>1787.43</v>
+      </c>
+      <c r="C266">
+        <v>119773.06</v>
+      </c>
+      <c r="D266">
+        <v>119773.06</v>
+      </c>
+      <c r="E266">
+        <v>7022.9501953125</v>
+      </c>
+      <c r="F266">
+        <v>1.179940938949585</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B267">
+        <v>1787.43</v>
+      </c>
+      <c r="C267">
+        <v>120135.77</v>
+      </c>
+      <c r="D267">
+        <v>120135.77</v>
+      </c>
+      <c r="E267">
+        <v>7041.27978515625</v>
+      </c>
+      <c r="F267">
+        <v>1.180916309356689</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B268">
+        <v>1787.43</v>
+      </c>
+      <c r="C268">
+        <v>121726.45</v>
+      </c>
+      <c r="D268">
+        <v>121726.45</v>
+      </c>
+      <c r="E268">
+        <v>7126.06005859375</v>
+      </c>
+      <c r="F268">
+        <v>1.176747441291809</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5755,7 +5755,207 @@
         <v>7126.06005859375</v>
       </c>
       <c r="F268">
-        <v>1.176747441291809</v>
+        <v>1.178272724151611</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B269">
+        <v>1787.43</v>
+      </c>
+      <c r="C269">
+        <v>113887.4204327393</v>
+      </c>
+      <c r="D269">
+        <v>113887.4204327393</v>
+      </c>
+      <c r="E269">
+        <v>7109.14013671875</v>
+      </c>
+      <c r="F269">
+        <v>1.174122333526611</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B270">
+        <v>7546.44</v>
+      </c>
+      <c r="C270">
+        <v>120551.68</v>
+      </c>
+      <c r="D270">
+        <v>120551.68</v>
+      </c>
+      <c r="E270">
+        <v>7064.009765625</v>
+      </c>
+      <c r="F270">
+        <v>1.178439259529114</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B271">
+        <v>7546.44</v>
+      </c>
+      <c r="C271">
+        <v>122496.65</v>
+      </c>
+      <c r="D271">
+        <v>122496.65</v>
+      </c>
+      <c r="E271">
+        <v>7137.89990234375</v>
+      </c>
+      <c r="F271">
+        <v>1.174425721168518</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46135</v>
+      </c>
+      <c r="B272">
+        <v>7546.44</v>
+      </c>
+      <c r="C272">
+        <v>121460.23</v>
+      </c>
+      <c r="D272">
+        <v>121460.23</v>
+      </c>
+      <c r="E272">
+        <v>7108.39990234375</v>
+      </c>
+      <c r="F272">
+        <v>1.17060375213623</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B273">
+        <v>7546.44</v>
+      </c>
+      <c r="C273">
+        <v>123129.27</v>
+      </c>
+      <c r="D273">
+        <v>123129.27</v>
+      </c>
+      <c r="E273">
+        <v>7165.080078125</v>
+      </c>
+      <c r="F273">
+        <v>1.16838800907135</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B274">
+        <v>7546.44</v>
+      </c>
+      <c r="C274">
+        <v>123489.2091345215</v>
+      </c>
+      <c r="D274">
+        <v>123489.2091345215</v>
+      </c>
+      <c r="E274">
+        <v>7173.91015625</v>
+      </c>
+      <c r="F274">
+        <v>1.170644879341125</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B275">
+        <v>7546.44</v>
+      </c>
+      <c r="C275">
+        <v>122597.86</v>
+      </c>
+      <c r="D275">
+        <v>122597.86</v>
+      </c>
+      <c r="E275">
+        <v>7138.7998046875</v>
+      </c>
+      <c r="F275">
+        <v>1.172346711158752</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B276">
+        <v>7546.44</v>
+      </c>
+      <c r="C276">
+        <v>124510.17</v>
+      </c>
+      <c r="D276">
+        <v>124510.17</v>
+      </c>
+      <c r="E276">
+        <v>7135.9501953125</v>
+      </c>
+      <c r="F276">
+        <v>1.171783447265625</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B277">
+        <v>7546.44</v>
+      </c>
+      <c r="C277">
+        <v>125999.07</v>
+      </c>
+      <c r="D277">
+        <v>125999.07</v>
+      </c>
+      <c r="E277">
+        <v>7209.009765625</v>
+      </c>
+      <c r="F277">
+        <v>1.168470025062561</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B278">
+        <v>7546.44</v>
+      </c>
+      <c r="C278">
+        <v>126878.23</v>
+      </c>
+      <c r="D278">
+        <v>126878.23</v>
+      </c>
+      <c r="E278">
+        <v>7230.1201171875</v>
+      </c>
+      <c r="F278">
+        <v>1.172333002090454</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5955,7 +5955,107 @@
         <v>7230.1201171875</v>
       </c>
       <c r="F278">
-        <v>1.172333002090454</v>
+        <v>1.172910451889038</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B279">
+        <v>7546.44</v>
+      </c>
+      <c r="C279">
+        <v>131332.9649481201</v>
+      </c>
+      <c r="D279">
+        <v>131332.9649481201</v>
+      </c>
+      <c r="E279">
+        <v>7200.75</v>
+      </c>
+      <c r="F279">
+        <v>1.172662854194641</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B280">
+        <v>2642.24</v>
+      </c>
+      <c r="C280">
+        <v>130848.63</v>
+      </c>
+      <c r="D280">
+        <v>130848.63</v>
+      </c>
+      <c r="E280">
+        <v>7259.22021484375</v>
+      </c>
+      <c r="F280">
+        <v>1.169194102287292</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B281">
+        <v>2642.24</v>
+      </c>
+      <c r="C281">
+        <v>133294.68</v>
+      </c>
+      <c r="D281">
+        <v>133294.68</v>
+      </c>
+      <c r="E281">
+        <v>7365.1201171875</v>
+      </c>
+      <c r="F281">
+        <v>1.171577453613281</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B282">
+        <v>2642.24</v>
+      </c>
+      <c r="C282">
+        <v>131477.21</v>
+      </c>
+      <c r="D282">
+        <v>131477.21</v>
+      </c>
+      <c r="E282">
+        <v>7337.10986328125</v>
+      </c>
+      <c r="F282">
+        <v>1.174743056297302</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B283">
+        <v>2642.24</v>
+      </c>
+      <c r="C283">
+        <v>137211.07</v>
+      </c>
+      <c r="D283">
+        <v>137211.07</v>
+      </c>
+      <c r="E283">
+        <v>7398.93017578125</v>
+      </c>
+      <c r="F283">
+        <v>1.178967237472534</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F283"/>
+  <dimension ref="A1:F288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6055,7 +6055,107 @@
         <v>7398.93017578125</v>
       </c>
       <c r="F283">
-        <v>1.178967237472534</v>
+        <v>1.173158168792725</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B284">
+        <v>2642.24</v>
+      </c>
+      <c r="C284">
+        <v>130978.9116918945</v>
+      </c>
+      <c r="D284">
+        <v>130978.9116918945</v>
+      </c>
+      <c r="E284">
+        <v>7412.83984375</v>
+      </c>
+      <c r="F284">
+        <v>1.176885962486267</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B285">
+        <v>10839.77</v>
+      </c>
+      <c r="C285">
+        <v>137125.16</v>
+      </c>
+      <c r="D285">
+        <v>137125.16</v>
+      </c>
+      <c r="E285">
+        <v>7400.9599609375</v>
+      </c>
+      <c r="F285">
+        <v>1.177994966506958</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B286">
+        <v>10839.77</v>
+      </c>
+      <c r="C286">
+        <v>138254.75</v>
+      </c>
+      <c r="D286">
+        <v>138254.75</v>
+      </c>
+      <c r="E286">
+        <v>7444.25</v>
+      </c>
+      <c r="F286">
+        <v>1.173543691635132</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B287">
+        <v>10839.77</v>
+      </c>
+      <c r="C287">
+        <v>138462.65</v>
+      </c>
+      <c r="D287">
+        <v>138462.65</v>
+      </c>
+      <c r="E287">
+        <v>7501.240234375</v>
+      </c>
+      <c r="F287">
+        <v>1.171604990959167</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B288">
+        <v>10839.77</v>
+      </c>
+      <c r="C288">
+        <v>135427.31</v>
+      </c>
+      <c r="D288">
+        <v>135427.31</v>
+      </c>
+      <c r="E288">
+        <v>7408.5</v>
+      </c>
+      <c r="F288">
+        <v>1.163061261177063</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6155,7 +6155,107 @@
         <v>7408.5</v>
       </c>
       <c r="F288">
-        <v>1.163061261177063</v>
+        <v>1.166208028793335</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B289">
+        <v>10839.77</v>
+      </c>
+      <c r="C289">
+        <v>134242.2850756836</v>
+      </c>
+      <c r="D289">
+        <v>134242.2850756836</v>
+      </c>
+      <c r="E289">
+        <v>7403.0498046875</v>
+      </c>
+      <c r="F289">
+        <v>1.161440134048462</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B290">
+        <v>10839.77</v>
+      </c>
+      <c r="C290">
+        <v>134394.74</v>
+      </c>
+      <c r="D290">
+        <v>134394.74</v>
+      </c>
+      <c r="E290">
+        <v>7353.60986328125</v>
+      </c>
+      <c r="F290">
+        <v>1.165514707565308</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B291">
+        <v>10839.77</v>
+      </c>
+      <c r="C291">
+        <v>137443.94</v>
+      </c>
+      <c r="D291">
+        <v>137443.94</v>
+      </c>
+      <c r="E291">
+        <v>7432.97021484375</v>
+      </c>
+      <c r="F291">
+        <v>1.160712242126465</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B292">
+        <v>10839.77</v>
+      </c>
+      <c r="C292">
+        <v>138989.33</v>
+      </c>
+      <c r="D292">
+        <v>138989.33</v>
+      </c>
+      <c r="E292">
+        <v>7445.72021484375</v>
+      </c>
+      <c r="F292">
+        <v>1.16253387928009</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B293">
+        <v>10839.77</v>
+      </c>
+      <c r="C293">
+        <v>140659.46</v>
+      </c>
+      <c r="D293">
+        <v>140659.46</v>
+      </c>
+      <c r="E293">
+        <v>7473.47021484375</v>
+      </c>
+      <c r="F293">
+        <v>1.160496711730957</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_values_app.xlsx
+++ b/portfolio_values_app.xlsx
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F293"/>
+  <dimension ref="A1:F310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6255,7 +6255,347 @@
         <v>7473.47021484375</v>
       </c>
       <c r="F293">
-        <v>1.160496711730957</v>
+        <v>1.162115097045898</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B294">
+        <v>10839.77</v>
+      </c>
+      <c r="C294">
+        <v>145662.9221148682</v>
+      </c>
+      <c r="D294">
+        <v>145662.9221148682</v>
+      </c>
+      <c r="E294">
+        <v>7519.1201171875</v>
+      </c>
+      <c r="F294">
+        <v>1.163737893104553</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B295">
+        <v>10839.77</v>
+      </c>
+      <c r="C295">
+        <v>146397.5</v>
+      </c>
+      <c r="D295">
+        <v>146397.5</v>
+      </c>
+      <c r="E295">
+        <v>7520.35986328125</v>
+      </c>
+      <c r="F295">
+        <v>1.163683772087097</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B296">
+        <v>10839.77</v>
+      </c>
+      <c r="C296">
+        <v>146633.12</v>
+      </c>
+      <c r="D296">
+        <v>146633.12</v>
+      </c>
+      <c r="E296">
+        <v>7563.6298828125</v>
+      </c>
+      <c r="F296">
+        <v>1.16179096698761</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B297">
+        <v>10839.77</v>
+      </c>
+      <c r="C297">
+        <v>148136.93</v>
+      </c>
+      <c r="D297">
+        <v>148136.93</v>
+      </c>
+      <c r="E297">
+        <v>7580.06005859375</v>
+      </c>
+      <c r="F297">
+        <v>1.165283799171448</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B298">
+        <v>10839.77</v>
+      </c>
+      <c r="C298">
+        <v>150465.4070391846</v>
+      </c>
+      <c r="D298">
+        <v>150465.4070391846</v>
+      </c>
+      <c r="E298">
+        <v>7599.9599609375</v>
+      </c>
+      <c r="F298">
+        <v>1.164890170097351</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B299">
+        <v>10839.77</v>
+      </c>
+      <c r="C299">
+        <v>150465.41</v>
+      </c>
+      <c r="D299">
+        <v>150465.41</v>
+      </c>
+      <c r="E299">
+        <v>7609.77978515625</v>
+      </c>
+      <c r="F299">
+        <v>1.163548350334167</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B300">
+        <v>10839.77</v>
+      </c>
+      <c r="C300">
+        <v>151414.82</v>
+      </c>
+      <c r="D300">
+        <v>151414.82</v>
+      </c>
+      <c r="E300">
+        <v>7553.68017578125</v>
+      </c>
+      <c r="F300">
+        <v>1.162209630012512</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B301">
+        <v>10839.77</v>
+      </c>
+      <c r="C301">
+        <v>149606.09</v>
+      </c>
+      <c r="D301">
+        <v>149606.09</v>
+      </c>
+      <c r="E301">
+        <v>7584.31005859375</v>
+      </c>
+      <c r="F301">
+        <v>1.160941243171692</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B302">
+        <v>10839.77</v>
+      </c>
+      <c r="C302">
+        <v>143840.33</v>
+      </c>
+      <c r="D302">
+        <v>143840.33</v>
+      </c>
+      <c r="E302">
+        <v>7383.740234375</v>
+      </c>
+      <c r="F302">
+        <v>1.161264896392822</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B303">
+        <v>10839.77</v>
+      </c>
+      <c r="C303">
+        <v>146369.7850756836</v>
+      </c>
+      <c r="D303">
+        <v>146369.7850756836</v>
+      </c>
+      <c r="E303">
+        <v>7405.72998046875</v>
+      </c>
+      <c r="F303">
+        <v>1.152259588241577</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B304">
+        <v>10839.77</v>
+      </c>
+      <c r="C304">
+        <v>145843.1</v>
+      </c>
+      <c r="D304">
+        <v>145843.1</v>
+      </c>
+      <c r="E304">
+        <v>7386.64990234375</v>
+      </c>
+      <c r="F304">
+        <v>1.152844071388245</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B305">
+        <v>10839.77</v>
+      </c>
+      <c r="C305">
+        <v>142932.5</v>
+      </c>
+      <c r="D305">
+        <v>142932.5</v>
+      </c>
+      <c r="E305">
+        <v>7266.990234375</v>
+      </c>
+      <c r="F305">
+        <v>1.153535604476929</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B306">
+        <v>10839.77</v>
+      </c>
+      <c r="C306">
+        <v>147762.71</v>
+      </c>
+      <c r="D306">
+        <v>147762.71</v>
+      </c>
+      <c r="E306">
+        <v>7394.2998046875</v>
+      </c>
+      <c r="F306">
+        <v>1.153562188148499</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B307">
+        <v>10839.77</v>
+      </c>
+      <c r="C307">
+        <v>148317.11</v>
+      </c>
+      <c r="D307">
+        <v>148317.11</v>
+      </c>
+      <c r="E307">
+        <v>7431.4599609375</v>
+      </c>
+      <c r="F307">
+        <v>1.157594919204712</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B308">
+        <v>10839.77</v>
+      </c>
+      <c r="C308">
+        <v>151061.3874621582</v>
+      </c>
+      <c r="D308">
+        <v>151061.3874621582</v>
+      </c>
+      <c r="E308">
+        <v>7554.2900390625</v>
+      </c>
+      <c r="F308">
+        <v>1.160308122634888</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B309">
+        <v>10839.77</v>
+      </c>
+      <c r="C309">
+        <v>148511.15</v>
+      </c>
+      <c r="D309">
+        <v>148511.15</v>
+      </c>
+      <c r="E309">
+        <v>7511.35009765625</v>
+      </c>
+      <c r="F309">
+        <v>1.159420251846313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B310">
+        <v>10839.77</v>
+      </c>
+      <c r="C310">
+        <v>146965.76</v>
+      </c>
+      <c r="D310">
+        <v>146965.76</v>
+      </c>
+      <c r="E310">
+        <v>7420.10009765625</v>
+      </c>
+      <c r="F310">
+        <v>1.160995244979858</v>
       </c>
     </row>
   </sheetData>
